--- a/p6_deployment/data/germany/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/germany/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,6 +1347,28 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>GfN42CgJ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
